--- a/data/trans_orig/IP07A17-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A17-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2007 (tasa de respuesta: 98,3%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 98,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18720</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30023</t>
+          <t>29855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18390</t>
+          <t>18393</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29580</t>
+          <t>29067</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40001</t>
+          <t>40263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55959</t>
+          <t>55730</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27360</t>
+          <t>27244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26346</t>
+          <t>26807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34932</t>
+          <t>35049</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50934</t>
+          <t>51036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,46%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94014</t>
+          <t>94235</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116379</t>
+          <t>116547</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104312</t>
+          <t>106403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129859</t>
+          <t>129526</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>207661</t>
+          <t>206857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>240031</t>
+          <t>239884</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67654</t>
+          <t>67839</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90072</t>
+          <t>89855</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84457</t>
+          <t>84694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109842</t>
+          <t>108116</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158268</t>
+          <t>159133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>191433</t>
+          <t>192629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>20687</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12756</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25766</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24547</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42449</t>
+          <t>41776</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21164</t>
+          <t>21468</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34997</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19225</t>
+          <t>19832</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32154</t>
+          <t>31963</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42942</t>
+          <t>44771</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62002</t>
+          <t>63037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>50,44%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20143</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33819</t>
+          <t>34166</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18718</t>
+          <t>19212</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31129</t>
+          <t>31187</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42793</t>
+          <t>42528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60968</t>
+          <t>60410</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15022</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14682</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>26128</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>143677</t>
+          <t>143213</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>172006</t>
+          <t>171182</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149801</t>
+          <t>152519</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>181093</t>
+          <t>182295</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>305050</t>
+          <t>304942</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>344854</t>
+          <t>344240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113145</t>
+          <t>113682</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>140461</t>
+          <t>141886</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128459</t>
+          <t>127169</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>158308</t>
+          <t>157582</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>249463</t>
+          <t>248856</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>288571</t>
+          <t>289981</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>18580</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35177</t>
+          <t>34398</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37004</t>
+          <t>36560</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>43777</t>
+          <t>43999</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>66166</t>
+          <t>66589</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>776</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2012 (tasa de respuesta: 97,39%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28792</t>
+          <t>28123</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40158</t>
+          <t>40172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18412</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29477</t>
+          <t>29509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49459</t>
+          <t>50915</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65651</t>
+          <t>66709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18555</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23837</t>
+          <t>23904</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24430</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39431</t>
+          <t>39592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13975</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80865</t>
+          <t>80389</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104856</t>
+          <t>103575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107303</t>
+          <t>107176</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132658</t>
+          <t>132096</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>195992</t>
+          <t>195827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231712</t>
+          <t>229630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84478</t>
+          <t>84366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108463</t>
+          <t>108078</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73207</t>
+          <t>72925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97395</t>
+          <t>98219</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162720</t>
+          <t>164104</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198988</t>
+          <t>198262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,94%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>19632</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12417</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26336</t>
+          <t>25591</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23420</t>
+          <t>23002</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41111</t>
+          <t>40481</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>11152</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29086</t>
+          <t>30261</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41975</t>
+          <t>42738</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27686</t>
+          <t>27118</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39841</t>
+          <t>39945</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61880</t>
+          <t>60875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>78463</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,61%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12106</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24015</t>
+          <t>23960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28077</t>
+          <t>28380</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31179</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47513</t>
+          <t>48900</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>12130</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149047</t>
+          <t>148993</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178784</t>
+          <t>177753</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163386</t>
+          <t>162006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>193089</t>
+          <t>191181</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>320082</t>
+          <t>320716</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>363289</t>
+          <t>364353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,1%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112005</t>
+          <t>110896</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141238</t>
+          <t>140418</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108979</t>
+          <t>111806</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>138869</t>
+          <t>139177</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>232619</t>
+          <t>230053</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>271028</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32253</t>
+          <t>32227</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31105</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35303</t>
+          <t>34678</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57558</t>
+          <t>57100</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15194</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>591</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2016 (tasa de respuesta: 97,64%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 97,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21469</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16887</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22205</t>
+          <t>21657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35594</t>
+          <t>35703</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16886</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22133</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22823</t>
+          <t>22387</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35878</t>
+          <t>36012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11737</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>127177</t>
+          <t>127793</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>153440</t>
+          <t>154317</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124777</t>
+          <t>124237</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149568</t>
+          <t>150990</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>261237</t>
+          <t>261484</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297162</t>
+          <t>296857</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74289</t>
+          <t>74790</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100162</t>
+          <t>99931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70199</t>
+          <t>69309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94038</t>
+          <t>94122</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>152377</t>
+          <t>152008</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187366</t>
+          <t>186794</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21222</t>
+          <t>21954</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12412</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>26277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42246</t>
+          <t>42713</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6955</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32151</t>
+          <t>31600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45765</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43685</t>
+          <t>42245</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56835</t>
+          <t>56874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79773</t>
+          <t>79633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98907</t>
+          <t>99365</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,17%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22940</t>
+          <t>23145</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>37662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>13858</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27164</t>
+          <t>27174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40801</t>
+          <t>40222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59670</t>
+          <t>59857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1692</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14458</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180801</t>
+          <t>181307</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>211375</t>
+          <t>211832</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>184981</t>
+          <t>185812</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>215282</t>
+          <t>216843</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>373874</t>
+          <t>373451</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>419120</t>
+          <t>420754</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>114830</t>
+          <t>116219</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>144470</t>
+          <t>145909</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103881</t>
+          <t>102355</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132224</t>
+          <t>130885</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>225974</t>
+          <t>224757</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>268154</t>
+          <t>269772</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14322</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>28857</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>18576</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35387</t>
+          <t>35018</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36872</t>
+          <t>37595</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>59589</t>
+          <t>59272</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12664</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17934</t>
+          <t>18016</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A17-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A17-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 98,3%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 98,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23808</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18222</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29561</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,41%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38,58%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>24467</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18856</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>29855</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18874</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>30196</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>48,88%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,64%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>23808</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>18393</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>29067</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>50,41%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40263</t>
+          <t>40786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55730</t>
+          <t>56147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,71%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20815</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15309</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26718</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21640</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27244</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16141</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27684</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>43,23%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>54,43%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20815</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15838</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>26807</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>44,07%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35049</t>
+          <t>34977</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51036</t>
+          <t>50133</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>51,53%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2662</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5998</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6613</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,32%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3003</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4437</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3235</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3650</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4719</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -1179,102 +1179,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3340</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>647</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3549</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3277</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3344</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3948</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>50057</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>50057</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>50057</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>117612</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>105338</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>129645</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50,17%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>105511</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>94235</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>116547</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>94476</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>115905</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>52,62%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>58,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>117612</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>106403</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>129526</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>50,17%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206857</t>
+          <t>206640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>239884</t>
+          <t>240952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>96850</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>85479</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>108816</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,31%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>36,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>78192</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67839</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>89855</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>67908</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>89921</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,99%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,81%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>96850</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>84694</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>108116</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,31%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159133</t>
+          <t>158239</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192629</t>
+          <t>192770</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,32%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17950</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12352</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>25164</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,73%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>14140</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8945</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>20687</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8776</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>20797</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,05%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,32%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>17950</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>12323</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>25634</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24964</t>
+          <t>24601</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41776</t>
+          <t>41011</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4769</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1912</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5176</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5406</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,95%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1379</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4165</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1861,102 +1861,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3249</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>778</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4183</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4321</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3283</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4541</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4918</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>234438</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>234438</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>234438</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200534</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200534</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200534</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>234438</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>234438</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>234438</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25582</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19569</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31888</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>42,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>32,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>53,41%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>28027</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>21468</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34939</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>21340</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>34493</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>42,93%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,89%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>25582</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>19832</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>31963</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>42,85%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44771</t>
+          <t>43866</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63037</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>24809</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>18856</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>31313</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>41,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,59%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>52,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>20273</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34166</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>20280</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>33617</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>41,41%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>52,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>24809</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>19212</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>31187</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>41,56%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42528</t>
+          <t>43903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60410</t>
+          <t>61845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -2317,67 +2317,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>9308</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5469</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>14416</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15,59%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9,16%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>24,15%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>9535</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5352</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>14842</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5763</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>15419</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>14,61%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>22,74%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>9308</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>5324</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>14706</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>15,59%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>25697</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -2425,107 +2425,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3957</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2777</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59699</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59699</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59699</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>65278</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>65278</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>65278</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59699</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59699</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59699</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>167002</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>153068</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>181278</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>48,92%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>44,84%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>53,1%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>158005</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>143213</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>171182</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>143602</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>171284</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>50,02%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>45,34%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>54,19%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>167002</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>152519</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>182295</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>48,92%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>304942</t>
+          <t>303123</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>344240</t>
+          <t>344636</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>142474</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>128918</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>156647</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>41,74%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>37,77%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>45,89%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>126865</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>113682</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>141886</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>113858</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>141124</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>40,16%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>44,92%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>142474</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>127169</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>157582</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>41,74%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248856</t>
+          <t>249691</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>289981</t>
+          <t>289851</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -2994,64 +2994,64 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>27851</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>20710</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>36982</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10,83%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>26337</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>18580</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>34398</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>19135</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>35219</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>8,34%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>27851</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>20677</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>36560</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>6,06%</t>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>43999</t>
+          <t>44681</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>66589</t>
+          <t>67164</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6825</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>3237</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1212</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1177</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6946</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2726</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>6814</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3225,67 +3225,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3965</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>1425</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4603</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4388</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>341367</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>341367</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>341367</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>469</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>315869</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>315869</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>315869</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>341367</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>341367</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>341367</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,39%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23896</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18196</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29717</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,84%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40,23%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>65,71%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>34661</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28123</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40172</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>28523</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>39865</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>65,3%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>23896</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>18360</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>29509</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,84%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50915</t>
+          <t>50623</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66709</t>
+          <t>66516</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,66%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18165</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12557</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23886</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>13320</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8584</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18653</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8892</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19387</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>25,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,17%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18165</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12686</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23904</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>40,17%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24659</t>
+          <t>24196</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39592</t>
+          <t>38971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3166</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1222</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6523</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,42%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5102</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2271</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10489</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9946</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>9,61%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3166</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1222</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6661</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13617</t>
+          <t>14141</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45227</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45227</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45227</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45227</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45227</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45227</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>120239</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>108283</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>131922</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52,88%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>92363</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>80389</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>103575</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>80021</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>104191</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>45,24%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,38%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>120239</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>107176</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>132096</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>52,88%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>195827</t>
+          <t>194681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>229630</t>
+          <t>229124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>84714</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>72995</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>96222</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,1%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>95948</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>84366</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>108078</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>84186</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>107674</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>47,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>41,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>52,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>84714</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>72925</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>98219</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,26%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164104</t>
+          <t>164710</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198262</t>
+          <t>197526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18343</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12603</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26699</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,74%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>12370</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8004</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19632</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>19011</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,06%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,62%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18343</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>12370</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>25591</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>22855</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40481</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3447</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7533</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2222</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5967</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7187</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3447</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7827</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11152</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -4815,72 +4815,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3292</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1250</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4736</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4273</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3860</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>227389</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>227389</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>227389</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>292</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>204153</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>204153</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>204153</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>227389</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>227389</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>227389</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5050,67 +5050,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>33955</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27359</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39801</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>58,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,7%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>36472</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30261</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>42738</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>29180</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42276</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>59,15%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>49,08%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>69,32%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33955</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>27118</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>39945</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>58,61%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60875</t>
+          <t>62066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78463</t>
+          <t>78553</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,69%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21807</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15937</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>28182</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>37,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>27,51%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>48,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>17331</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11848</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23960</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>24300</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>28,11%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19,22%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,86%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>21807</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>16284</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>28380</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>37,64%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31560</t>
+          <t>31229</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48900</t>
+          <t>47032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3769</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>5686</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2455</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10773</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2470</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>11401</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>9,22%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>3356</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>12020</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -5389,67 +5389,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>1499</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9,06%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>1494</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>5196</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1499</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4829</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>763</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -5497,107 +5497,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3419</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3347</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3768</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61658</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61658</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61658</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>178088</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>162717</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>191845</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>53,88%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>49,23%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>58,04%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>163495</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>148993</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>177753</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>149545</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>178287</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>51,27%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>46,72%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>55,74%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>178088</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>162006</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>191181</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>53,88%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>320716</t>
+          <t>321747</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>364353</t>
+          <t>361939</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>124687</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>111956</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>139783</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>37,72%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>42,29%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>126599</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>110896</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>140418</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>111357</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>140956</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>39,7%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>34,78%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>44,03%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>124687</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>111806</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>139177</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>37,72%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>230053</t>
+          <t>232519</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>271028</t>
+          <t>271608</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>22181</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>15281</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>31175</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>23158</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>16158</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>32227</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>15669</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>31744</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>7,26%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>22181</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>16184</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>30314</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34678</t>
+          <t>35106</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57100</t>
+          <t>57354</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4946</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2190</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>9936</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>3715</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1384</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>9142</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1424</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8542</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>4946</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2142</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>9856</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -6179,72 +6179,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3628</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>1925</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5173</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5054</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3408</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>330548</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>330548</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>330548</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>453</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>318893</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>318893</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>318893</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>330548</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>330548</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>330548</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 97,64%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 97,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12334</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7856</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16932</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>16596</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11931</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21142</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21369</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>52,17%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12334</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7644</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17317</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>33,66%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21657</t>
+          <t>22622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35703</t>
+          <t>35719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16347</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11568</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21252</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>58,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12492</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8316</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17504</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8190</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16968</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,26%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>55,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16347</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11639</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21619</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>44,62%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22387</t>
+          <t>22835</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36012</t>
+          <t>35482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3466</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7340</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20,03%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5973</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7037</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>8,57%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3466</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1352</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7980</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10959</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -6979,92 +6979,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3158</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>3158</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7162</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3158</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>7254</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -7092,107 +7092,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4171</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1333</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4799</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4660</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4398</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>137640</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>124697</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>150491</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>51,59%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>140809</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>127793</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>154317</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>128469</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>153679</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>56,9%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>51,64%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>137640</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>124237</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>150990</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>56,94%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>261484</t>
+          <t>261414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>296857</t>
+          <t>296690</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,65%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>81456</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>69723</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>94739</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>87531</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>74790</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>99931</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>75489</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>99312</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>35,37%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,38%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>81456</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>69309</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>94122</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>33,7%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>152008</t>
+          <t>152389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186794</t>
+          <t>185403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,9%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18286</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>25570</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>14372</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9164</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>21954</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>9086</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>21402</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,81%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,87%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18286</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>12470</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>26277</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,57%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>23937</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42713</t>
+          <t>42141</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -7666,67 +7666,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2820</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6440</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>3278</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>982</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8302</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8222</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2820</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7045</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>11365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -7779,67 +7779,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1508</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5922</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>1481</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6167</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4926</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1508</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5235</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>241710</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>241710</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>241710</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>356</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>247471</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>247471</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>247471</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>241710</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>241710</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>241710</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>50721</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43675</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>57388</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>66,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>57,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>75,11%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>38940</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>31600</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>45539</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>31799</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>45455</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>52,8%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>61,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>50721</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>42245</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>56874</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>66,39%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79633</t>
+          <t>79946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99365</t>
+          <t>100283</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19775</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14023</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>26760</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25,88%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18,35%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,03%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>29757</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>23145</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>37662</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>23217</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>37061</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>40,35%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,06%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>19775</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>13858</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>27174</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>25,88%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>40474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59857</t>
+          <t>59710</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1678</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9553</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3584</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>7389</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7832</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,86%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>4558</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1692</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>9510</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14252</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -8348,102 +8348,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3598</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>638</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3221</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3271</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3626</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3878</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1273</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4473</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -8461,102 +8461,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3544</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>836</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4376</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3606</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5981</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1549</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>5302</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>76402</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>76402</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>76402</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>73754</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>73754</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>73754</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>76402</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>76402</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>76402</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>200694</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>184646</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>215639</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>56,57%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>52,05%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>60,79%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>196345</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>181307</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>211832</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>181412</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>213035</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>55,62%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>51,36%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>60,0%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>200694</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>185812</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>216843</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>373451</t>
+          <t>375575</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>420754</t>
+          <t>419851</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>117579</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>104214</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>133825</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>33,14%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>29,38%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>37,72%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>129779</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>116219</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>145909</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>114745</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>145077</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>36,76%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>32,92%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>41,33%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>117579</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>102355</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>130885</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>33,14%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>224757</t>
+          <t>226244</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>269772</t>
+          <t>273048</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>26310</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>19079</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>35593</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>20682</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>14322</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>28857</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>14473</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>29576</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>5,86%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>26310</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>18576</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>35018</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>37595</t>
+          <t>37168</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>59272</t>
+          <t>59956</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6613</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2994</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>12207</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>3916</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1460</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>8701</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8524</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>6613</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>3143</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>11926</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -9138,72 +9138,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3554</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>8380</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>2317</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5949</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>6163</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3554</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>7890</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>354749</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>354749</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>354749</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>505</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>353039</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>353039</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>353039</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>354749</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>354749</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>354749</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
